--- a/Project9/表單/煉獄庭園BGM分類.xlsx
+++ b/Project9/表單/煉獄庭園BGM分類.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10">
   <si>
     <t>曲名</t>
   </si>
@@ -29,6 +29,24 @@
   <si>
     <t>悲傷</t>
   </si>
+  <si>
+    <t>death tone</t>
+  </si>
+  <si>
+    <t>悲傷後振奮</t>
+  </si>
+  <si>
+    <t>winter tears</t>
+  </si>
+  <si>
+    <t>悲壯</t>
+  </si>
+  <si>
+    <t>終わりに遺るもの</t>
+  </si>
+  <si>
+    <t>燃 戰鬥</t>
+  </si>
 </sst>
 </file>
 
@@ -36,8 +54,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -49,6 +67,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="新細明體"/>
@@ -59,6 +91,89 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="新細明體"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -73,22 +188,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -102,31 +202,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="新細明體"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -134,67 +212,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="新細明體"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="新細明體"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -209,13 +227,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -227,19 +359,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,25 +377,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -281,19 +389,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,91 +401,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -400,6 +418,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -427,17 +454,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -459,20 +482,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -491,162 +518,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -997,8 +1015,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelRow="4" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="20.4285714285714" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1014,6 +1035,30 @@
       </c>
       <c r="B2" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
